--- a/artfynd/A 31268-2025 artfynd.xlsx
+++ b/artfynd/A 31268-2025 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">

--- a/artfynd/A 31268-2025 artfynd.xlsx
+++ b/artfynd/A 31268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112814802</v>
+        <v>115283562</v>
       </c>
       <c r="B2" t="n">
-        <v>90340</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>413</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Huvudlik svampklubba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Tolypocladium capitatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Holmsk.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326788</v>
+        <v>327122</v>
       </c>
       <c r="R2" t="n">
-        <v>6549618</v>
+        <v>6549932</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,24 +754,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -793,44 +772,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112814810</v>
+        <v>113695685</v>
       </c>
       <c r="B3" t="n">
-        <v>91217</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
@@ -840,10 +821,10 @@
         <v>327143</v>
       </c>
       <c r="R3" t="n">
-        <v>6549927</v>
+        <v>6549921</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,68 +862,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>sara lindh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Larsson, sara lindh</t>
+          <t>sara lindh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112814808</v>
+        <v>112814804</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327146</v>
+        <v>326939</v>
       </c>
       <c r="R4" t="n">
-        <v>6549924</v>
+        <v>6549772</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,15 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112814804</v>
+        <v>113760099</v>
       </c>
       <c r="B5" t="n">
-        <v>91191</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,24 +1010,23 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>326939</v>
+        <v>326781</v>
       </c>
       <c r="R5" t="n">
-        <v>6549772</v>
+        <v>6549667</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,18 +1064,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>sara lindh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Larsson, sara lindh</t>
+          <t>sara lindh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1110,12 +1086,7 @@
         <v>112814803</v>
       </c>
       <c r="B6" t="n">
-        <v>91195</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,7 +1118,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>326924</v>
+        <v>326925</v>
       </c>
       <c r="R6" t="n">
         <v>6549763</v>
@@ -1209,47 +1180,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112814811</v>
+        <v>112814810</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327137</v>
+        <v>327143</v>
       </c>
       <c r="R7" t="n">
         <v>6549927</v>
@@ -1311,56 +1281,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113367008</v>
+        <v>112814802</v>
       </c>
       <c r="B8" t="n">
-        <v>91608</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003297</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327143</v>
+        <v>326788</v>
       </c>
       <c r="R8" t="n">
-        <v>6549921</v>
+        <v>6549618</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,38 +1346,48 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>sara lindh</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>sara lindh</t>
+          <t>Anton Larsson, sara lindh</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1425,16 +1397,11 @@
         <v>113695780</v>
       </c>
       <c r="B9" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1447,12 +1414,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1532,64 +1499,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113695685</v>
+        <v>112814808</v>
       </c>
       <c r="B10" t="n">
-        <v>91607</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327143</v>
+        <v>327147</v>
       </c>
       <c r="R10" t="n">
-        <v>6549921</v>
+        <v>6549924</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,12 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,75 +1578,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>sara lindh</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>sara lindh</t>
+          <t>Anton Larsson, sara lindh</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113760099</v>
+        <v>112814811</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rammberget, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>326781</v>
+        <v>327137</v>
       </c>
       <c r="R11" t="n">
-        <v>6549667</v>
+        <v>6549927</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,12 +1661,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,34 +1675,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>sara lindh</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>sara lindh</t>
+          <t>Anton Larsson, sara lindh</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115283562</v>
+        <v>112814812</v>
       </c>
       <c r="B12" t="n">
-        <v>84117</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,21 +1704,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>413</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huvudlik svampklubba</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tolypocladium capitatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Holmsk.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1792,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>327122</v>
+        <v>326818</v>
       </c>
       <c r="R12" t="n">
-        <v>6549932</v>
+        <v>6549591</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,6 +1787,112 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113367008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6003297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spricktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rammberget, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>327143</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6549921</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>sara lindh</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>sara lindh</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31268-2025 artfynd.xlsx
+++ b/artfynd/A 31268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113695685</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814804</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113760099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814803</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814810</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814802</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113695780</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814808</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814811</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814812</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,8 +1953,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367008</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>